--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
     </row>
@@ -11368,22 +11368,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,29 +11393,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,29 +11425,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,29 +11457,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,29 +11489,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,29 +11521,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,29 +11553,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,29 +11617,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11661,17 +11661,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,29 +11681,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11713,29 +11713,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11757,17 +11757,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,29 +11777,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,29 +11809,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11853,17 +11853,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -11885,17 +11885,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,29 +11905,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11937,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11981,17 +11981,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -12013,17 +12013,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12033,29 +12033,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
@@ -12109,17 +12109,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -12141,17 +12141,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -12173,17 +12173,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,29 +12193,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,29 +12225,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,29 +12257,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -12328,22 +12328,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12424,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12456,22 +12456,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12493,17 +12493,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12552,22 +12552,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
     </row>
@@ -11368,22 +11368,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,29 +11393,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,29 +11425,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,29 +11457,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
@@ -11501,17 +11501,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,29 +11521,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,29 +11585,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -11629,17 +11629,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11666,12 +11666,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,29 +11681,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11713,29 +11713,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,29 +11745,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,29 +11777,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11821,17 +11821,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,29 +11841,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,29 +11873,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
@@ -11917,17 +11917,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11937,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11981,17 +11981,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,14 +12001,14 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12065,29 +12065,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -12114,12 +12114,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,29 +12129,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,29 +12161,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,14 +12193,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,29 +12225,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
@@ -12269,17 +12269,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12360,22 +12360,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12424,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12456,22 +12456,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12488,22 +12488,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12552,22 +12552,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -11368,22 +11368,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,29 +11393,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
@@ -11437,17 +11437,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,29 +11457,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11501,17 +11501,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,29 +11521,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,29 +11553,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,29 +11585,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11634,12 +11634,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11661,17 +11661,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11698,12 +11698,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11713,14 +11713,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,29 +11745,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,29 +11777,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,29 +11809,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -11853,17 +11853,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,14 +11873,14 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,29 +11905,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11937,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
@@ -11986,12 +11986,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -12013,17 +12013,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12033,29 +12033,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12065,29 +12065,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12097,29 +12097,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,29 +12129,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,29 +12161,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,29 +12193,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -12237,17 +12237,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
@@ -12274,12 +12274,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -12328,22 +12328,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12360,22 +12360,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12424,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12456,22 +12456,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12488,22 +12488,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12552,22 +12552,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>大连机场保时捷中心</t>
+          <t>大连华南保时捷中心</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>大连市甘井子区虹城路570号</t>
+          <t>甘井子区华东路129号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大连华南保时捷中心</t>
+          <t>大连机场保时捷中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>甘井子区华东路129号</t>
+          <t>大连市甘井子区虹城路570号</t>
         </is>
       </c>
     </row>
@@ -11368,22 +11368,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,29 +11393,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,14 +11425,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -11442,12 +11442,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
@@ -11469,17 +11469,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11501,17 +11501,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
@@ -11533,17 +11533,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
@@ -11565,17 +11565,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11629,17 +11629,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11661,17 +11661,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11693,17 +11693,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11713,29 +11713,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,29 +11745,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,29 +11777,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,29 +11809,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11853,17 +11853,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,29 +11873,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -11922,12 +11922,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11937,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11981,17 +11981,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,29 +12001,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
@@ -12045,17 +12045,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -12077,17 +12077,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12097,14 +12097,14 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,29 +12129,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,29 +12161,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,29 +12193,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,29 +12225,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,29 +12257,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
@@ -12328,22 +12328,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12360,22 +12360,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12392,22 +12392,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12424,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12456,22 +12456,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12488,22 +12488,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12520,22 +12520,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12552,22 +12552,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>大连华南保时捷中心</t>
+          <t>大连机场保时捷中心</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>甘井子区华东路129号</t>
+          <t>大连市甘井子区虹城路570号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大连机场保时捷中心</t>
+          <t>大连华南保时捷中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>大连市甘井子区虹城路570号</t>
+          <t>甘井子区华东路129号</t>
         </is>
       </c>
     </row>
@@ -11373,17 +11373,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11410,12 +11410,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,29 +11457,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,14 +11489,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -11506,12 +11506,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,29 +11521,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,29 +11553,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,29 +11617,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,29 +11649,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
@@ -11720,22 +11720,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,29 +11745,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -11789,17 +11789,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11821,17 +11821,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,29 +11841,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,29 +11873,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11922,12 +11922,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11937,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
@@ -11981,17 +11981,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,29 +12001,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12033,29 +12033,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -12109,17 +12109,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,29 +12129,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12178,12 +12178,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,29 +12193,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,29 +12225,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
@@ -12269,17 +12269,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
@@ -12328,22 +12328,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12360,22 +12360,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12397,17 +12397,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12424,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12461,17 +12461,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12488,22 +12488,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12520,22 +12520,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12552,22 +12552,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8634</v>
+        <v>8636</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8626</v>
+        <v>8628</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-8</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="3" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="3" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -6628,19 +6628,19 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C273" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E273" s="3" t="n">
         <v>0</v>
@@ -6649,19 +6649,19 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C274" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E274" s="3" t="n">
         <v>0</v>
@@ -6675,14 +6675,14 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C275" s="3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D275" s="3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E275" s="3" t="n">
         <v>0</v>
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E276" s="3" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E278" s="3" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E279" s="3" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E280" s="3" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E281" s="3" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E282" s="3" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E283" s="3" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E284" s="3" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E285" s="3" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E286" s="3" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E287" s="3" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E288" s="3" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E289" s="3" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="E290" s="3" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E291" s="3" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E292" s="3" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E293" s="3" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E294" s="3" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E295" s="3" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E296" s="3" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E297" s="3" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E298" s="3" t="n">
         <v>0</v>
@@ -7179,59 +7179,59 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E299" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C299" s="3" t="n">
+      <c r="C301" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D299" s="3" t="n">
+      <c r="D301" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E299" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="D300" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="E300" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C301" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D301" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="E301" s="4" t="n">
-        <v>1</v>
+      <c r="E301" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -7242,59 +7242,59 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E302" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
           <t>江西</t>
         </is>
       </c>
-      <c r="C302" s="4" t="n">
+      <c r="C304" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D302" s="4" t="n">
+      <c r="D304" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E302" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B303" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C303" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D303" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E303" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C304" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D304" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E304" s="3" t="n">
-        <v>0</v>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7305,14 +7305,14 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E305" s="3" t="n">
         <v>0</v>
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E306" s="3" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E307" s="3" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E308" s="3" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E309" s="3" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E310" s="3" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D311" s="3" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E311" s="3" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="E312" s="3" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E313" s="3" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E314" s="3" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E315" s="3" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D316" s="3" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="E316" s="3" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="D317" s="3" t="n">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="E317" s="3" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E318" s="3" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E319" s="3" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D320" s="3" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E320" s="3" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D321" s="3" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="E321" s="3" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D322" s="3" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="E322" s="3" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E323" s="3" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E324" s="3" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E325" s="3" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E326" s="3" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D327" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E327" s="3" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E328" s="3" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E329" s="3" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E330" s="3" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E331" s="3" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D332" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E332" s="3" t="n">
         <v>0</v>
@@ -7893,101 +7893,101 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D333" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D334" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C333" s="3" t="n">
+      <c r="C335" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D333" s="3" t="n">
+      <c r="D335" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="E333" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="inlineStr">
+      <c r="E335" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B334" s="2" t="inlineStr">
+      <c r="B336" s="2" t="inlineStr">
         <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n">
+      <c r="C336" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="D334" s="2" t="n">
+      <c r="D336" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="E334" s="2" t="n">
+      <c r="E336" s="2" t="n">
         <v>-2</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B335" s="2" t="inlineStr">
+      <c r="B337" s="2" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
+      <c r="C337" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="D335" s="2" t="n">
+      <c r="D337" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="E335" s="2" t="n">
+      <c r="E337" s="2" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C336" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D336" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E336" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B337" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C337" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D337" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E337" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E338" s="3" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D339" s="3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E339" s="3" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D340" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E340" s="3" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D341" s="3" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E341" s="3" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D342" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E342" s="3" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E344" s="3" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E345" s="3" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E346" s="3" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="E347" s="3" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E348" s="3" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D349" s="3" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E349" s="3" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E350" s="3" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E351" s="3" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E352" s="3" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E353" s="3" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D354" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E356" s="3" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E357" s="3" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E358" s="3" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E359" s="3" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D360" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E360" s="3" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D361" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E361" s="3" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E362" s="3" t="n">
         <v>0</v>
@@ -8523,14 +8523,14 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D363" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E363" s="3" t="n">
         <v>0</v>
@@ -8539,19 +8539,19 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D364" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E364" s="3" t="n">
         <v>0</v>
@@ -8560,19 +8560,19 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C365" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D365" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E365" s="3" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C366" s="3" t="n">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D368" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E368" s="3" t="n">
         <v>0</v>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="3" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="3" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
@@ -8749,19 +8749,19 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E374" s="3" t="n">
         <v>0</v>
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E375" s="3" t="n">
         <v>0</v>
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E376" s="3" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E377" s="3" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E378" s="3" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" s="3" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E380" s="3" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E381" s="3" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E382" s="3" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E383" s="3" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E384" s="3" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E385" s="3" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="3" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="3" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E387" s="3" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="3" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="3" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="3" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="3" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="3" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="3" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="3" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="3" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="3" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="3" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="3" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="3" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="3" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="3" t="n">
         <v>0</v>
@@ -9363,59 +9363,59 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D403" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C403" s="3" t="n">
+      <c r="C405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D403" s="3" t="n">
+      <c r="D405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E403" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B404" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C404" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="D404" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="E404" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="2" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C405" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D405" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E405" s="2" t="n">
-        <v>-1</v>
+      <c r="E405" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>93</v>
+        <v>207</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="407">
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D407" s="2" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E407" s="2" t="n">
         <v>-1</v>
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C408" s="2" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D408" s="2" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E408" s="2" t="n">
         <v>-1</v>
@@ -9489,59 +9489,59 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="inlineStr">
+      <c r="A410" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C410" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="D410" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E410" s="3" t="n">
-        <v>0</v>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="3" t="inlineStr">
+      <c r="A411" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B411" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C411" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="D411" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="E411" s="3" t="n">
-        <v>0</v>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="412">
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E412" s="3" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E426" s="3" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E427" s="3" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E428" s="3" t="n">
         <v>0</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C429" s="3" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E429" s="3" t="n">
         <v>0</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E430" s="3" t="n">
         <v>0</v>
@@ -9951,59 +9951,59 @@
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D431" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E431" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D432" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E432" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C431" s="3" t="n">
+      <c r="C433" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D431" s="3" t="n">
+      <c r="D433" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E431" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B432" s="4" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C432" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D432" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="E432" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B433" s="4" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C433" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D433" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="E433" s="4" t="n">
-        <v>1</v>
+      <c r="E433" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>湖南</t>
         </is>
       </c>
-      <c r="C434" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="D434" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="E434" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10083,7 +10125,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10098,7 +10140,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10152,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10125,7 +10167,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10179,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10152,7 +10194,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10206,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10179,7 +10221,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10233,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10206,7 +10248,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10341,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10314,7 +10356,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10368,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10341,7 +10383,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10659,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>大连机场保时捷中心</t>
+          <t>大连华南保时捷中心</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -10632,7 +10674,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>大连市甘井子区虹城路570号</t>
+          <t>甘井子区华东路129号</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10686,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大连华南保时捷中心</t>
+          <t>大连机场保时捷中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10659,7 +10701,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>甘井子区华东路129号</t>
+          <t>大连市甘井子区虹城路570号</t>
         </is>
       </c>
     </row>
@@ -11368,22 +11410,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11393,7 +11435,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -11410,12 +11452,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11425,7 +11467,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11437,17 +11479,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11457,29 +11499,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11489,29 +11531,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11521,29 +11563,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11553,7 +11595,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
@@ -11570,12 +11612,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11585,29 +11627,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11617,7 +11659,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
@@ -11629,17 +11671,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11649,29 +11691,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11681,7 +11723,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11693,17 +11735,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11713,7 +11755,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11772,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11745,29 +11787,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11777,7 +11819,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11789,17 +11831,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11809,29 +11851,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11841,7 +11883,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11853,17 +11895,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11873,14 +11915,14 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -11890,12 +11932,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11905,29 +11947,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11937,29 +11979,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -11969,7 +12011,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11986,12 +12028,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12001,7 +12043,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12072,22 +12114,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12097,29 +12139,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12129,7 +12171,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -12141,17 +12183,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12161,29 +12203,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12193,29 +12235,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12225,7 +12267,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -12237,17 +12279,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12257,29 +12299,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12289,7 +12331,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -12328,22 +12370,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12360,22 +12402,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12397,17 +12439,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12424,22 +12466,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12456,22 +12498,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12488,22 +12530,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12520,22 +12562,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12557,17 +12599,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10341,7 +10341,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>大连华南保时捷中心</t>
+          <t>大连机场保时捷中心</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>甘井子区华东路129号</t>
+          <t>大连市甘井子区虹城路570号</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大连机场保时捷中心</t>
+          <t>大连华南保时捷中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>大连市甘井子区虹城路570号</t>
+          <t>甘井子区华东路129号</t>
         </is>
       </c>
     </row>
@@ -11410,22 +11410,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11447,17 +11447,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11467,29 +11467,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11499,29 +11499,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11531,29 +11531,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11563,29 +11563,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11595,29 +11595,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11659,29 +11659,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11703,17 +11703,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11723,29 +11723,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11755,29 +11755,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -11799,17 +11799,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11831,17 +11831,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11851,29 +11851,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11883,29 +11883,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11927,17 +11927,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11947,29 +11947,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11979,29 +11979,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
@@ -12023,17 +12023,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -12055,17 +12055,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12075,29 +12075,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12139,29 +12139,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12171,29 +12171,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12203,14 +12203,14 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -12220,12 +12220,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12235,29 +12235,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12267,29 +12267,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -12316,12 +12316,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -12375,17 +12375,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12439,17 +12439,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12466,22 +12466,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12498,22 +12498,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12530,22 +12530,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12572,12 +12572,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12594,22 +12594,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10125,7 +10125,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
     </row>
@@ -11410,22 +11410,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11435,29 +11435,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
@@ -11479,17 +11479,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11511,17 +11511,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11531,29 +11531,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11563,29 +11563,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11595,29 +11595,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11659,29 +11659,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11703,17 +11703,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11723,29 +11723,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11755,29 +11755,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11787,29 +11787,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
@@ -11831,17 +11831,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11863,17 +11863,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -11895,17 +11895,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11915,29 +11915,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11947,29 +11947,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11979,29 +11979,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12011,29 +12011,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12043,29 +12043,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -12092,12 +12092,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -12119,17 +12119,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -12151,17 +12151,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
@@ -12188,12 +12188,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12203,14 +12203,14 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -12220,12 +12220,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -12279,17 +12279,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -12311,17 +12311,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -12370,22 +12370,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12434,22 +12434,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12466,22 +12466,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12498,22 +12498,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12530,22 +12530,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12567,17 +12567,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12594,22 +12594,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（26家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（23家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,14 +518,14 @@
         <v>97</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.1%</t>
         </is>
       </c>
     </row>
@@ -665,14 +665,14 @@
         <v>848</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -683,10 +683,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>3</v>
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8636</v>
+        <v>8637</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8628</v>
+        <v>8632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="3">
@@ -4435,10 +4435,10 @@
         <v>46</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="169">
@@ -4470,38 +4470,38 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D171" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E171" s="2" t="n">
-        <v>-1</v>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -4512,14 +4512,14 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E172" s="3" t="n">
         <v>0</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E173" s="3" t="n">
         <v>0</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E174" s="3" t="n">
         <v>0</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E175" s="3" t="n">
         <v>0</v>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E176" s="3" t="n">
         <v>0</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E177" s="3" t="n">
         <v>0</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E178" s="3" t="n">
         <v>0</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="E179" s="3" t="n">
         <v>0</v>
@@ -4680,14 +4680,14 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="E180" s="3" t="n">
         <v>0</v>
@@ -4701,14 +4701,14 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="E181" s="3" t="n">
         <v>0</v>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="C210" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E210" s="3" t="n">
         <v>0</v>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10088,6 +10088,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10116,6 +10117,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -10125,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10140,7 +10146,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10167,7 +10178,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10194,7 +10210,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10224,6 +10245,11 @@
           <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -10251,6 +10277,11 @@
           <t>瑶光路8号</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10278,6 +10309,11 @@
           <t>江西省新余市北湖西路158号恒太城购物中心南大门</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -10305,6 +10341,11 @@
           <t>百盛购物中心L1层1号门中庭</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -10332,6 +10373,11 @@
           <t>山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -10359,6 +10405,11 @@
           <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -10386,6 +10437,11 @@
           <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -10413,6 +10469,11 @@
           <t>湖南省长沙市雨花区黎托街道长沙大道567号运达汇一楼L138A</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -10440,6 +10501,11 @@
           <t>上海市长宁区长宁路1018号中山公园龙之梦1F1046</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10467,6 +10533,11 @@
           <t>广东省珠海市香洲区银桦路102号珠海万象汇L1层L137商铺</t>
         </is>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10494,6 +10565,11 @@
           <t>江西省南昌市红谷滩区红谷滩万达广场1层1039/1050号铺位</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10521,6 +10597,11 @@
           <t>广西壮族自治区柳州市柳南区汇轮路广西汽车贸易园内1-2号</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10548,6 +10629,11 @@
           <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10575,6 +10661,11 @@
           <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -10600,6 +10691,11 @@
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>贵州省六盘水市钟山区钟山西路白鹤高架桥北侧汽车文化广场（临时营业）</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10622,6 +10718,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10650,6 +10747,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10677,6 +10779,11 @@
           <t>大连市甘井子区虹城路570号</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10686,7 +10793,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大连华南保时捷中心</t>
+          <t>沈阳铁西保时捷中心</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -10696,39 +10803,49 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>大连市</t>
+          <t>沈阳市</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>甘井子区华东路129号</t>
+          <t>辽宁省沈阳市铁西区北二西路21号</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沈阳铁西保时捷中心</t>
+          <t>天津市鹏龙九州汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>沈阳市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>辽宁省沈阳市铁西区北二西路21号</t>
+          <t>北辰区小淀镇外环东路与规划丹河道交口</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -10740,49 +10857,59 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>天津市鹏龙九州汽车销售服务有限公司</t>
+          <t>襄阳恒信巨星汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>襄阳市</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>北辰区小淀镇外环东路与规划丹河道交口</t>
+          <t>襄州区春园东路189号2幢</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>襄阳恒信巨星汽车销售服务有限公司</t>
+          <t>小米汽车云南玉溪红塔区玉溪三千城购物公园</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>襄阳市</t>
+          <t>玉溪市</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>襄州区春园东路189号2幢</t>
+          <t>云南省玉溪市红塔区河滨路1号三千城悦容汇购物公园一楼1号门入口TB103点位</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -10794,22 +10921,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南玉溪红塔区玉溪三千城购物公园</t>
+          <t>小米汽车湖北恩施和润城</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>玉溪市</t>
+          <t>恩施土家族苗族自治州</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>云南省玉溪市红塔区河滨路1号三千城悦容汇购物公园一楼1号门入口TB103点位</t>
+          <t>和润城A馆中庭</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -10821,22 +10953,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广西贵港港北区贵港万达</t>
+          <t>小米汽车湖北武汉汉阳区武汉经开永旺</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>贵港市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>布山大道1500号万达广场1F5号门小中庭</t>
+          <t>经开永旺梦乐城A馆一楼8号门直行中央广场</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -10848,22 +10985,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省宜昌市宜都市宜都万达</t>
+          <t>小米汽车湖南岳阳岳阳楼区岳阳步步高新天地</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>宜昌市</t>
+          <t>岳阳市</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>湖北省宜昌市宜都市陆城宜华大道102号宜都万达1F中庭</t>
+          <t>步步高新天地L1层</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -10875,169 +11017,199 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施和润城</t>
+          <t>小米汽车黑龙江哈尔滨松北区哈尔滨融创茂</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>恩施土家族苗族自治州</t>
+          <t>哈尔滨市</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>和润城A馆中庭</t>
+          <t>黑龙江省哈尔滨市松北区世茂大道99号融创茂1F中庭</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北武汉汉阳区武汉经开永旺</t>
+          <t>小鹏汽车肇庆敏捷广场销售中心</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>经开永旺梦乐城A馆一楼8号门直行中央广场</t>
+          <t>广东省肇庆市端州区信安大道3号敏捷广场1层1014铺</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖南岳阳岳阳楼区岳阳步步高新天地</t>
+          <t>深圳卓悦中心品牌体验店</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>岳阳市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>步步高新天地L1层</t>
+          <t>广东省深圳市福田区福华一路348号卓悦中心L135-L137铺位</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨松北区哈尔滨融创茂</t>
+          <t>温州国鼎永嘉卫星店</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市松北区世茂大道99号融创茂1F中庭</t>
+          <t>浙江省温州市永嘉县瓯北街道五星社区张堡东路瓯嘉汽车商业广场【B101-B103】号</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车肇庆敏捷广场销售中心</t>
+          <t>蔚来空间 | 无锡苏宁广场</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>广东省肇庆市端州区信安大道3号敏捷广场1层1014铺</t>
+          <t>江苏省无锡市梁溪区人民中路111号无锡苏宁广场1F110B</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>深圳卓悦中心品牌体验店</t>
+          <t>蔚来空间 | 常熟永旺</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区福华一路348号卓悦中心L135-L137铺位</t>
+          <t>江苏省苏州市常熟市虞新线西侧260米永旺梦乐城F3</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>温州国鼎永嘉卫星店</t>
+          <t>蔚来空间 | 杭州西湖</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -11047,93 +11219,113 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>杭州市</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县瓯北街道五星社区张堡东路瓯嘉汽车商业广场【B101-B103】号</t>
+          <t>浙江省杭州市上城区湖滨路18号杭州湖滨银泰in77店A区L1018-1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 无锡苏宁广场</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>长春市</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>江苏省无锡市梁溪区人民中路111号无锡苏宁广场1F110B</t>
+          <t>吉林省长春市汽开区景阳大路3862号</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 常熟永旺</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>眉山市</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市常熟市虞新线西侧260米永旺梦乐城F3</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州西湖</t>
+          <t>鸿蒙智行授权用户中心•吕梁聚富汽贸园</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市上城区湖滨路18号杭州湖滨银泰in77店A区L1018-1</t>
+          <t>山西省吕梁市离石区聚富汽贸园</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -11145,22 +11337,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>AITO授权用户中心·佛山北滘车城</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>长春市</t>
+          <t>佛山市</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号</t>
+          <t>广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -11172,22 +11369,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行尚界用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -11199,22 +11401,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•吕梁聚富汽贸园</t>
+          <t>鸿蒙智行尚界用户中心•信阳南京大道东</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>信阳市</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>山西省吕梁市离石区聚富汽贸园</t>
+          <t>河南省信阳市南京大道东段招商中心东300米路北（斯柯达）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -11226,22 +11433,27 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·佛山北滘车城</t>
+          <t>鸿蒙智行授权用户中心•武汉硚口新能源汽车园</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>佛山市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>湖北省武汉市硚口区工农路与惠安大道交汇处汉江湾C2地块</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
         </is>
       </c>
     </row>
@@ -11253,103 +11465,27 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行授权用户中心•安顺东冠汽车城</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>安顺市</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•信阳南京大道东</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>信阳市</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>河南省信阳市南京大道东段招商中心东300米路北（斯柯达）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•武汉硚口新能源汽车园</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>湖北省武汉市硚口区工农路与惠安大道交汇处汉江湾C2地块</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•安顺东冠汽车城</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>安顺市</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
           <t>贵州省安顺市西秀区新安街道产业园区大道1.5公里处</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -11415,17 +11551,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11435,29 +11571,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11467,7 +11603,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11479,17 +11615,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11499,7 +11635,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11511,17 +11647,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11531,29 +11667,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11563,29 +11699,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11595,7 +11731,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11612,12 +11748,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11627,7 +11763,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11775,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11659,29 +11795,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11691,7 +11827,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
@@ -11703,17 +11839,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11723,7 +11859,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11735,17 +11871,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11755,29 +11891,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11787,29 +11923,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11819,7 +11955,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11831,17 +11967,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11851,29 +11987,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11883,7 +12019,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11900,12 +12036,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11915,7 +12051,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11927,17 +12063,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11947,7 +12083,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11959,17 +12095,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11979,29 +12115,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12011,29 +12147,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12043,7 +12179,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -12055,17 +12191,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12075,29 +12211,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12107,7 +12243,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
@@ -12119,17 +12255,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12139,29 +12275,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12171,29 +12307,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12203,29 +12339,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12235,29 +12371,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12267,7 +12403,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
@@ -12306,22 +12442,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12331,7 +12467,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -12380,12 +12516,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12434,22 +12570,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12466,22 +12602,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12498,22 +12634,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12535,17 +12671,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12567,17 +12703,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12599,17 +12735,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10718,7 +10718,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>连续在档 10 期</t>
+          <t>连续在档 10 期；本期存在高相似店名「合肥恒信巨星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>连续在档 10 期</t>
+          <t>连续在档 10 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>连续在档 6 期</t>
+          <t>连续在档 6 期；本期存在高相似店名「鸿蒙智行智界用户中心•眉山眉州大道」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>连续在档 10 期</t>
+          <t>连续在档 10 期；本期存在高相似店名「AITO授权用户中心•佛山北滘车城」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>连续在档 10 期</t>
+          <t>连续在档 10 期；本期存在高相似店名「鸿蒙智行授权用户中心•深圳坪山锦龙大道」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>连续在档 10 期</t>
+          <t>连续在档 10 期；本期存在高相似店名「鸿蒙智行授权用户中心•信阳南京大道东」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>连续在档 10 期</t>
+          <t>连续在档 10 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11546,22 +11546,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11610,22 +11610,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>AITO授权用户中心•佛山北滘车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11699,14 +11699,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>华为智能生活馆•温州滨江万象城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
         </is>
       </c>
     </row>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>华为智能生活馆•长沙永旺梦乐城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>AITO授权用户中心•福州鼓楼</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
         </is>
       </c>
     </row>
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12307,29 +12307,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12339,29 +12339,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12371,29 +12371,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -12415,17 +12415,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12435,29 +12435,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -12506,22 +12506,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>AITO授权用户中心·成都龙潭汽车园</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>AITO授权用户中心•成都龙潭汽车园</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12543,17 +12543,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12570,22 +12570,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12602,22 +12602,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12634,22 +12634,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -12671,17 +12671,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -12703,17 +12703,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（23家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（38条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（14家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（17家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1715</v>
+        <v>1453</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1711</v>
+        <v>1451</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8637</v>
+        <v>8375</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8632</v>
+        <v>8372</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.0%</t>
         </is>
       </c>
     </row>
@@ -9426,17 +9426,17 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>207</v>
+        <v>38</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="407">
@@ -9447,101 +9447,101 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D407" s="2" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E407" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="2" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C408" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="D408" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="E408" s="2" t="n">
-        <v>-1</v>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="inlineStr">
+      <c r="A409" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B409" s="2" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C409" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D409" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="E409" s="2" t="n">
-        <v>-1</v>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E409" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="inlineStr">
+      <c r="A410" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="2" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C410" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="D410" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="E410" s="2" t="n">
-        <v>-1</v>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E410" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="inlineStr">
+      <c r="A411" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B411" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C411" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="D411" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="E411" s="2" t="n">
-        <v>-1</v>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C411" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D411" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E411" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="E412" s="3" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9745,10 +9745,10 @@
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="E426" s="3" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E427" s="3" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E428" s="3" t="n">
         <v>0</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C429" s="3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E429" s="3" t="n">
         <v>0</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="E430" s="3" t="n">
         <v>0</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C431" s="3" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D431" s="3" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="E431" s="3" t="n">
         <v>0</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D432" s="3" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E432" s="3" t="n">
         <v>0</v>
@@ -9993,80 +9993,80 @@
       </c>
       <c r="B433" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D433" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E433" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D434" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E434" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D435" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E435" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C433" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D433" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E433" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B434" s="4" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C434" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D434" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="E434" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B435" s="4" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C435" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D435" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="E435" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B436" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C436" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D436" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="E436" s="4" t="n">
-        <v>1</v>
+      <c r="C436" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D436" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E436" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10080,15 +10080,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10568,134 +10568,6 @@
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•柳州汽贸园</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>柳州市</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>广西壮族自治区柳州市柳南区汇轮路广西汽车贸易园内1-2号</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•邢台逗号立方</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>邢台市</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•长沙香江国际汽车城</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>长沙市</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•六盘水钟山</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>六盘水市</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>贵州省六盘水市钟山区钟山西路白鹤高架桥北侧汽车文化广场（临时营业）</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11241,27 +11113,27 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行授权用户中心•吕梁聚富汽贸园</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>长春市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号</t>
+          <t>山西省吕梁市离石区聚富汽贸园</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>连续在档 10 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 10 期</t>
         </is>
       </c>
     </row>
@@ -11273,219 +11145,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•武汉硚口新能源汽车园</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>湖北省武汉市硚口区工农路与惠安大道交汇处汉江湾C2地块</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>连续在档 6 期；本期存在高相似店名「鸿蒙智行智界用户中心•眉山眉州大道」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•吕梁聚富汽贸园</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>吕梁市</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>山西省吕梁市离石区聚富汽贸园</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 10 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心·佛山北滘车城</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>佛山市</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 10 期；本期存在高相似店名「AITO授权用户中心•佛山北滘车城」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•深圳坪山锦龙大道</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业）</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 10 期；本期存在高相似店名「鸿蒙智行授权用户中心•深圳坪山锦龙大道」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•信阳南京大道东</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>信阳市</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>河南省信阳市南京大道东段招商中心东300米路北（斯柯达）</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 10 期；本期存在高相似店名「鸿蒙智行授权用户中心•信阳南京大道东」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•武汉硚口新能源汽车园</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>湖北省武汉市硚口区工农路与惠安大道交汇处汉江湾C2地块</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
           <t>连续在档 1 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•安顺东冠汽车城</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>安顺市</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>贵州省安顺市西秀区新安街道产业园区大道1.5公里处</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 10 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11500,10 +11180,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
@@ -11546,22 +11226,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11571,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11603,29 +11283,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•佛山北滘车城</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11635,29 +11315,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省佛山市北滘镇碧江社区聚龙沙佛碧路2号之六 → 广东省佛山市顺德区北滘镇碧江聚龙沙佛碧路2号之六</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳坪山锦龙大道</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11667,29 +11347,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坪地街道中心社区龙岗大道（坪地段）1057号A1-02（临时营业） → 深圳市坪山区锦龙大道与坪山大道交叉口</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11699,29 +11379,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11731,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11763,29 +11443,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•长沙香江国际汽车城</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11795,29 +11475,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市开福区兴联路669号香江国际汽车城A馆一楼10193-10229商铺 → 湖南省长沙市开福区秀峰街道兴联路669号香江国际汽车城A馆一楼</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•西安凤城七路</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11827,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区凤城七路陕西商储物流园内 → 陕西省西安市未央区凤城七路陕西省物流集团内</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11859,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11876,12 +11556,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11891,14 +11571,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -11908,12 +11588,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•温州滨江万象城</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11923,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区瓯江路3999号 → 浙江省温州市鹿城区瓯江路3999号温州滨江万象城L1层115-116、L2层213</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11955,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11972,12 +11652,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11987,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12019,29 +11699,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市小店区大昌路73号 → 山西省太原市小店区唐槐产业园大昌路73号山西卡乐仕汽服装备院内左侧第4家</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•乌鲁木齐鲤鱼山北路</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12051,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐新市区八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号（临时营业） → 新疆乌鲁木齐高新区(新市区)八家户街道鲤鱼山北路1号新疆赛博特国际汽车城C5-1-01号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -12063,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12083,29 +11763,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•长沙永旺梦乐城</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12115,61 +11795,61 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号 → 湖南省长沙市长沙县星沙街道开元东路308号永旺梦乐城长沙星沙购物中心1层131铺位号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小米汽车山东省青岛市市北区交付中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小米汽车山东省青岛市市北区服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>小米汽车山东省青岛市市北区交付中心 → 小米汽车山东省青岛市市北区服务中心</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12179,29 +11859,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12211,29 +11891,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•福州鼓楼</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12243,29 +11923,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区梅峰路301号 → 福建省福州市闽侯县洪甘路189号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12275,29 +11955,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12307,29 +11987,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海世纪公园</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12339,14 +12019,14 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号A区 → 上海市浦东新区罗山路1589号C区</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -12356,12 +12036,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12370,390 +12050,6 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>奥迪</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>上海益申</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>上海益申</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车山东省青岛市市北区交付中心</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车山东省青岛市市北区服务中心</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车山东省青岛市市北区交付中心 → 小米汽车山东省青岛市市北区服务中心</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心·成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•成都龙潭汽车园</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>保时捷</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>南宁江南保时捷中心</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>南宁保时捷中心</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>太原沃之瑞卫星店</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>太原沃之瑞4S中心</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>太原沃之杰4S中心</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>太原沃之杰卫星店</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>温州国鼎4S中心</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>温州国鼎维修中心</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>地址归一前缀一致</t>
         </is>

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>-2</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8375</v>
+        <v>8374</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8372</v>
+        <v>8371</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-3</v>
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E430" s="3" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,29 +11347,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,29 +11443,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11620,12 +11620,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11652,12 +11652,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11748,12 +11748,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（14家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（17家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（14家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（17家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11322,22 +11322,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11428,12 +11428,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,29 +11443,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11620,12 +11620,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11652,12 +11652,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11738,22 +11738,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11780,12 +11780,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,29 +11251,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,29 +11315,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11428,12 +11428,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11652,12 +11652,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（14家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（17家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（14家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（17家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,29 +11251,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,29 +11379,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,29 +11603,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11652,12 +11652,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（14家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（17家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（14家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（17家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11268,12 +11268,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,29 +11379,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11492,12 +11492,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,29 +11603,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11652,12 +11652,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11258,22 +11258,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,29 +11315,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,29 +11603,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,29 +11251,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,29 +11283,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,29 +11315,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11620,12 +11620,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -11226,22 +11226,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,29 +11283,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11226,22 +11226,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11300,12 +11300,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,29 +11379,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11492,12 +11492,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11780,12 +11780,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
